--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_results_adapted_algorithm.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_results_adapted_algorithm.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK101"/>
+  <dimension ref="A1:AA101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,165 +439,115 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>HOMICIDE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SUICIDE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>HOMICIDE</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUICIDE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>PRELIM_OD</t>
+          <t>FINAL_OD</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>PRELIM_HEAT</t>
+          <t>FINAL_COLD</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>PRELIM_COLD</t>
+          <t>FINAL_HEAT</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>PRELIM_OTHER_INJURY</t>
+          <t>FINAL_SUICIDE_CAUSE</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>PRELIM_HOMICIDE</t>
+          <t>FINAL_HOMICIDE_CAUSE</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>PRELIM_SUICIDE</t>
+          <t>FINAL_OTHER_INJURY</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>PRELIM_HEART</t>
+          <t>FINAL_HEART</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>PRELIM_ILLNESS</t>
+          <t>FINAL_COMM_DISEASE</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>PRELIM_FIREARM</t>
+          <t>FINAL_NON_COMM_DISEASE</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>PRELIM_UNKNOWN</t>
+          <t>FINAL_ILLNESS</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>FINAL_ACC_OD</t>
+          <t>FINAL_UNDETERMINED_CAUSE</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>FINAL_ALL_OD</t>
+          <t>CAUSE_ACCIDENTAL</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>FINAL_HEAT</t>
+          <t>CAUSE_INTENTIONAL</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>FINAL_HEAT_UNK</t>
+          <t>CAUSE_EXTERNAL</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>FINAL_COLD</t>
+          <t>CAUSE_INTERNAL</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>FINAL_COLD_UNK</t>
+          <t>CAUSE_UNDETERMINED</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>FINAL_OTHER_INJURY</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
-        <is>
-          <t>FINAL_OTHER_INJURY_UNK</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>FINAL_HOMICIDE</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>FINAL_SUICIDE</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>FINAL_HEART</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>FINAL_HEART_UNK</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>FINAL_ILLNESS</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>FINAL_ILLNESS_UNK</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>FINAL_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>FINAL_UNKNOWN_UNK</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
         <is>
           <t>COD</t>
         </is>
@@ -620,10 +570,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -647,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -680,39 +630,9 @@
         <v>0</v>
       </c>
       <c r="Z2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -793,39 +713,9 @@
         <v>0</v>
       </c>
       <c r="Z3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -859,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -883,13 +773,13 @@
         <v>0</v>
       </c>
       <c r="Q4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -904,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="b">
         <v>0</v>
@@ -912,38 +802,8 @@
       <c r="Z4" t="b">
         <v>0</v>
       </c>
-      <c r="AA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
+      <c r="AA4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -976,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1000,13 +860,13 @@
         <v>0</v>
       </c>
       <c r="Q5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -1021,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="b">
         <v>0</v>
@@ -1029,38 +889,8 @@
       <c r="Z5" t="b">
         <v>0</v>
       </c>
-      <c r="AA5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
+      <c r="AA5" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1093,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1117,13 +947,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -1138,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
@@ -1146,38 +976,8 @@
       <c r="Z6" t="b">
         <v>0</v>
       </c>
-      <c r="AA6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
+      <c r="AA6" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1257,39 +1057,9 @@
         <v>0</v>
       </c>
       <c r="Z7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1370,39 +1140,9 @@
         <v>0</v>
       </c>
       <c r="Z8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1432,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1483,39 +1223,9 @@
         <v>0</v>
       </c>
       <c r="Z9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1545,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1596,39 +1306,9 @@
         <v>0</v>
       </c>
       <c r="Z10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1646,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -1658,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1709,39 +1389,9 @@
         <v>0</v>
       </c>
       <c r="Z11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1759,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -1771,7 +1421,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1822,39 +1472,9 @@
         <v>0</v>
       </c>
       <c r="Z12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1931,39 +1551,9 @@
         <v>0</v>
       </c>
       <c r="Z13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1997,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2021,13 +1611,13 @@
         <v>0</v>
       </c>
       <c r="Q14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
@@ -2042,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="b">
         <v>0</v>
@@ -2050,38 +1640,8 @@
       <c r="Z14" t="b">
         <v>0</v>
       </c>
-      <c r="AA14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
+      <c r="AA14" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -2110,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2161,39 +1721,9 @@
         <v>0</v>
       </c>
       <c r="Z15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2211,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -2223,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2274,39 +1804,9 @@
         <v>0</v>
       </c>
       <c r="Z16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2324,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
@@ -2387,39 +1887,9 @@
         <v>0</v>
       </c>
       <c r="Z17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2437,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
@@ -2449,7 +1919,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2500,39 +1970,9 @@
         <v>0</v>
       </c>
       <c r="Z18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2553,10 +1993,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -2580,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -2613,39 +2053,9 @@
         <v>0</v>
       </c>
       <c r="Z19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2675,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2726,39 +2136,9 @@
         <v>0</v>
       </c>
       <c r="Z20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2776,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -2788,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2839,39 +2219,9 @@
         <v>0</v>
       </c>
       <c r="Z21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2889,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -2901,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2952,39 +2302,9 @@
         <v>0</v>
       </c>
       <c r="Z22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3018,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -3069,39 +2389,9 @@
         <v>0</v>
       </c>
       <c r="Z23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3135,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -3186,39 +2476,9 @@
         <v>0</v>
       </c>
       <c r="Z24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3299,39 +2559,9 @@
         <v>0</v>
       </c>
       <c r="Z25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3365,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3389,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="Q26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="b">
         <v>0</v>
@@ -3410,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="b">
         <v>0</v>
@@ -3418,38 +2648,8 @@
       <c r="Z26" t="b">
         <v>0</v>
       </c>
-      <c r="AA26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
+      <c r="AA26" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -3482,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3506,13 +2706,13 @@
         <v>0</v>
       </c>
       <c r="Q27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="b">
         <v>0</v>
@@ -3527,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="X27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="b">
         <v>0</v>
@@ -3535,38 +2735,8 @@
       <c r="Z27" t="b">
         <v>0</v>
       </c>
-      <c r="AA27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
+      <c r="AA27" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -3595,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3646,39 +2816,9 @@
         <v>0</v>
       </c>
       <c r="Z28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3708,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3759,39 +2899,9 @@
         <v>0</v>
       </c>
       <c r="Z29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3825,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3876,39 +2986,9 @@
         <v>0</v>
       </c>
       <c r="Z30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3942,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -3966,13 +3046,13 @@
         <v>0</v>
       </c>
       <c r="Q31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="b">
         <v>0</v>
@@ -3987,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="X31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="b">
         <v>0</v>
@@ -3995,38 +3075,8 @@
       <c r="Z31" t="b">
         <v>0</v>
       </c>
-      <c r="AA31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
+      <c r="AA31" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -4040,7 +3090,7 @@
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -4106,39 +3156,9 @@
         <v>0</v>
       </c>
       <c r="Z32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4219,39 +3239,9 @@
         <v>0</v>
       </c>
       <c r="Z33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4285,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
@@ -4312,10 +3302,10 @@
         <v>1</v>
       </c>
       <c r="R34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" t="b">
         <v>0</v>
@@ -4330,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="X34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="b">
         <v>0</v>
@@ -4338,38 +3328,8 @@
       <c r="Z34" t="b">
         <v>0</v>
       </c>
-      <c r="AA34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
+      <c r="AA34" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -4398,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -4449,39 +3409,9 @@
         <v>0</v>
       </c>
       <c r="Z35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4515,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
@@ -4539,13 +3469,13 @@
         <v>0</v>
       </c>
       <c r="Q36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="b">
         <v>0</v>
@@ -4560,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="X36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="b">
         <v>0</v>
@@ -4568,38 +3498,8 @@
       <c r="Z36" t="b">
         <v>0</v>
       </c>
-      <c r="AA36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
+      <c r="AA36" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -4632,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -4659,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -4677,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="b">
         <v>0</v>
@@ -4685,38 +3585,8 @@
       <c r="Z37" t="b">
         <v>0</v>
       </c>
-      <c r="AA37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
+      <c r="AA37" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -4745,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
@@ -4796,39 +3666,9 @@
         <v>0</v>
       </c>
       <c r="Z38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4862,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
@@ -4886,13 +3726,13 @@
         <v>0</v>
       </c>
       <c r="Q39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" t="b">
         <v>0</v>
@@ -4907,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="X39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="b">
         <v>0</v>
@@ -4915,38 +3755,8 @@
       <c r="Z39" t="b">
         <v>0</v>
       </c>
-      <c r="AA39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
+      <c r="AA39" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -4975,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
@@ -5026,39 +3836,9 @@
         <v>0</v>
       </c>
       <c r="Z40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5079,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="b">
         <v>0</v>
@@ -5139,39 +3919,9 @@
         <v>0</v>
       </c>
       <c r="Z41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5205,7 +3955,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
@@ -5232,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -5250,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="X42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="b">
         <v>0</v>
@@ -5258,38 +4008,8 @@
       <c r="Z42" t="b">
         <v>0</v>
       </c>
-      <c r="AA42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
+      <c r="AA42" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -5318,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
@@ -5369,39 +4089,9 @@
         <v>0</v>
       </c>
       <c r="Z43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5416,7 +4106,7 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -5482,39 +4172,9 @@
         <v>0</v>
       </c>
       <c r="Z44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5544,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
@@ -5595,39 +4255,9 @@
         <v>0</v>
       </c>
       <c r="Z45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5657,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
@@ -5708,39 +4338,9 @@
         <v>0</v>
       </c>
       <c r="Z46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5821,39 +4421,9 @@
         <v>0</v>
       </c>
       <c r="Z47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5871,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
@@ -5883,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
@@ -5934,39 +4504,9 @@
         <v>0</v>
       </c>
       <c r="Z48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5996,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
@@ -6047,39 +4587,9 @@
         <v>0</v>
       </c>
       <c r="Z49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6097,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -6109,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
@@ -6160,39 +4670,9 @@
         <v>0</v>
       </c>
       <c r="Z50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6273,39 +4753,9 @@
         <v>0</v>
       </c>
       <c r="Z51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6335,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
@@ -6386,39 +4836,9 @@
         <v>0</v>
       </c>
       <c r="Z52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6436,7 +4856,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -6448,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
@@ -6499,39 +4919,9 @@
         <v>0</v>
       </c>
       <c r="Z53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6549,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -6561,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
@@ -6612,39 +5002,9 @@
         <v>0</v>
       </c>
       <c r="Z54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6725,39 +5085,9 @@
         <v>0</v>
       </c>
       <c r="Z55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6787,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
@@ -6838,39 +5168,9 @@
         <v>0</v>
       </c>
       <c r="Z56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6900,7 +5200,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -6951,39 +5251,9 @@
         <v>0</v>
       </c>
       <c r="Z57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7013,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -7064,39 +5334,9 @@
         <v>0</v>
       </c>
       <c r="Z58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7126,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
@@ -7177,39 +5417,9 @@
         <v>0</v>
       </c>
       <c r="Z59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7286,39 +5496,9 @@
         <v>0</v>
       </c>
       <c r="Z60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7348,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
@@ -7399,39 +5579,9 @@
         <v>0</v>
       </c>
       <c r="Z61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7465,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -7492,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="R62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" t="b">
         <v>0</v>
@@ -7510,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="X62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y62" t="b">
         <v>0</v>
@@ -7518,38 +5668,8 @@
       <c r="Z62" t="b">
         <v>0</v>
       </c>
-      <c r="AA62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>0</v>
+      <c r="AA62" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -7578,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -7629,39 +5749,9 @@
         <v>0</v>
       </c>
       <c r="Z63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7679,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
@@ -7691,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -7742,39 +5832,9 @@
         <v>0</v>
       </c>
       <c r="Z64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7808,7 +5868,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -7859,39 +5919,9 @@
         <v>0</v>
       </c>
       <c r="Z65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7925,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -7952,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="R66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -7970,7 +6000,7 @@
         <v>0</v>
       </c>
       <c r="X66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y66" t="b">
         <v>0</v>
@@ -7978,38 +6008,8 @@
       <c r="Z66" t="b">
         <v>0</v>
       </c>
-      <c r="AA66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>0</v>
+      <c r="AA66" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -8042,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -8066,13 +6066,13 @@
         <v>1</v>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" t="b">
         <v>0</v>
@@ -8087,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="X67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y67" t="b">
         <v>0</v>
@@ -8095,38 +6095,8 @@
       <c r="Z67" t="b">
         <v>0</v>
       </c>
-      <c r="AA67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ67" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>0</v>
+      <c r="AA67" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -8202,39 +6172,9 @@
         <v>0</v>
       </c>
       <c r="Z68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8252,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
@@ -8264,7 +6204,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
@@ -8315,39 +6255,9 @@
         <v>0</v>
       </c>
       <c r="Z69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8424,39 +6334,9 @@
         <v>0</v>
       </c>
       <c r="Z70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8537,39 +6417,9 @@
         <v>0</v>
       </c>
       <c r="Z71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8603,7 +6453,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
@@ -8630,7 +6480,7 @@
         <v>0</v>
       </c>
       <c r="R72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" t="b">
         <v>0</v>
@@ -8648,7 +6498,7 @@
         <v>0</v>
       </c>
       <c r="X72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y72" t="b">
         <v>0</v>
@@ -8656,38 +6506,8 @@
       <c r="Z72" t="b">
         <v>0</v>
       </c>
-      <c r="AA72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ72" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>0</v>
+      <c r="AA72" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="73">
@@ -8720,7 +6540,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
@@ -8771,39 +6591,9 @@
         <v>0</v>
       </c>
       <c r="Z73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8880,39 +6670,9 @@
         <v>0</v>
       </c>
       <c r="Z74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
@@ -8970,13 +6730,13 @@
         <v>0</v>
       </c>
       <c r="Q75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" t="b">
         <v>0</v>
@@ -8991,7 +6751,7 @@
         <v>0</v>
       </c>
       <c r="X75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y75" t="b">
         <v>0</v>
@@ -8999,38 +6759,8 @@
       <c r="Z75" t="b">
         <v>0</v>
       </c>
-      <c r="AA75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ75" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>0</v>
+      <c r="AA75" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="76">
@@ -9047,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="b">
         <v>0</v>
@@ -9059,7 +6789,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
@@ -9110,39 +6840,9 @@
         <v>0</v>
       </c>
       <c r="Z76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9176,7 +6876,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
@@ -9200,13 +6900,13 @@
         <v>0</v>
       </c>
       <c r="Q77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77" t="b">
         <v>0</v>
@@ -9221,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="X77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y77" t="b">
         <v>0</v>
@@ -9229,38 +6929,8 @@
       <c r="Z77" t="b">
         <v>0</v>
       </c>
-      <c r="AA77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK77" t="n">
-        <v>0</v>
+      <c r="AA77" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="78">
@@ -9277,7 +6947,7 @@
         <v>0</v>
       </c>
       <c r="E78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
@@ -9289,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" t="b">
         <v>0</v>
@@ -9340,39 +7010,9 @@
         <v>0</v>
       </c>
       <c r="Z78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ78" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9449,39 +7089,9 @@
         <v>0</v>
       </c>
       <c r="Z79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9499,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="E80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
@@ -9511,7 +7121,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
@@ -9562,39 +7172,9 @@
         <v>0</v>
       </c>
       <c r="Z80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9624,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
@@ -9675,39 +7255,9 @@
         <v>0</v>
       </c>
       <c r="Z81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9731,7 +7281,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="b">
         <v>0</v>
@@ -9788,39 +7338,9 @@
         <v>0</v>
       </c>
       <c r="Z82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ82" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9838,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="b">
         <v>0</v>
@@ -9850,7 +7370,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="b">
         <v>0</v>
@@ -9901,39 +7421,9 @@
         <v>0</v>
       </c>
       <c r="Z83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ83" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10010,39 +7500,9 @@
         <v>0</v>
       </c>
       <c r="Z84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10119,39 +7579,9 @@
         <v>0</v>
       </c>
       <c r="Z85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10166,7 +7596,7 @@
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
@@ -10232,39 +7662,9 @@
         <v>0</v>
       </c>
       <c r="Z86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10298,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
@@ -10322,13 +7722,13 @@
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" t="b">
         <v>0</v>
@@ -10343,7 +7743,7 @@
         <v>0</v>
       </c>
       <c r="X87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y87" t="b">
         <v>0</v>
@@ -10351,38 +7751,8 @@
       <c r="Z87" t="b">
         <v>0</v>
       </c>
-      <c r="AA87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ87" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK87" t="n">
-        <v>0</v>
+      <c r="AA87" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -10411,7 +7781,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="b">
         <v>0</v>
@@ -10462,39 +7832,9 @@
         <v>0</v>
       </c>
       <c r="Z88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ88" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10512,7 +7852,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="b">
         <v>0</v>
@@ -10524,7 +7864,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
@@ -10575,39 +7915,9 @@
         <v>0</v>
       </c>
       <c r="Z89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ89" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10628,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="F90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="b">
         <v>0</v>
@@ -10655,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="O90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P90" t="b">
         <v>0</v>
@@ -10688,39 +7998,9 @@
         <v>0</v>
       </c>
       <c r="Z90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10741,7 +8021,7 @@
         <v>0</v>
       </c>
       <c r="F91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="b">
         <v>0</v>
@@ -10801,39 +8081,9 @@
         <v>0</v>
       </c>
       <c r="Z91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ91" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10863,7 +8113,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="b">
         <v>0</v>
@@ -10914,39 +8164,9 @@
         <v>0</v>
       </c>
       <c r="Z92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ92" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10980,7 +8200,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="b">
         <v>0</v>
@@ -11007,7 +8227,7 @@
         <v>0</v>
       </c>
       <c r="R93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S93" t="b">
         <v>0</v>
@@ -11025,7 +8245,7 @@
         <v>0</v>
       </c>
       <c r="X93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y93" t="b">
         <v>0</v>
@@ -11033,38 +8253,8 @@
       <c r="Z93" t="b">
         <v>0</v>
       </c>
-      <c r="AA93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK93" t="n">
-        <v>0</v>
+      <c r="AA93" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="94">
@@ -11093,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="b">
         <v>0</v>
@@ -11144,39 +8334,9 @@
         <v>0</v>
       </c>
       <c r="Z94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11210,7 +8370,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="b">
         <v>1</v>
@@ -11252,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="W95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X95" t="b">
         <v>0</v>
@@ -11263,38 +8423,8 @@
       <c r="Z95" t="b">
         <v>0</v>
       </c>
-      <c r="AA95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK95" t="n">
-        <v>0</v>
+      <c r="AA95" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -11323,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="b">
         <v>0</v>
@@ -11374,39 +8504,9 @@
         <v>0</v>
       </c>
       <c r="Z96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ96" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11440,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="b">
         <v>0</v>
@@ -11464,13 +8564,13 @@
         <v>0</v>
       </c>
       <c r="Q97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97" t="b">
         <v>0</v>
@@ -11485,7 +8585,7 @@
         <v>0</v>
       </c>
       <c r="X97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y97" t="b">
         <v>0</v>
@@ -11493,38 +8593,8 @@
       <c r="Z97" t="b">
         <v>0</v>
       </c>
-      <c r="AA97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ97" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK97" t="n">
-        <v>0</v>
+      <c r="AA97" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="98">
@@ -11600,39 +8670,9 @@
         <v>0</v>
       </c>
       <c r="Z98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ98" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11666,7 +8706,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="b">
         <v>0</v>
@@ -11690,13 +8730,13 @@
         <v>1</v>
       </c>
       <c r="Q99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T99" t="b">
         <v>0</v>
@@ -11711,7 +8751,7 @@
         <v>0</v>
       </c>
       <c r="X99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y99" t="b">
         <v>0</v>
@@ -11719,38 +8759,8 @@
       <c r="Z99" t="b">
         <v>0</v>
       </c>
-      <c r="AA99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ99" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK99" t="n">
-        <v>0</v>
+      <c r="AA99" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -11826,39 +8836,9 @@
         <v>0</v>
       </c>
       <c r="Z100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ100" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11873,7 +8853,7 @@
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="b">
         <v>0</v>
@@ -11939,39 +8919,9 @@
         <v>0</v>
       </c>
       <c r="Z101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA101" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_results_adapted_algorithm.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_results_adapted_algorithm.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA101"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,36 +519,6 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>CAUSE_ACCIDENTAL</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>CAUSE_INTENTIONAL</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>CAUSE_EXTERNAL</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>CAUSE_INTERNAL</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>CAUSE_UNDETERMINED</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
           <t>COD</t>
         </is>
       </c>
@@ -614,25 +584,7 @@
       <c r="T2" t="b">
         <v>0</v>
       </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W2" t="b">
-        <v>0</v>
-      </c>
-      <c r="X2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="U2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -697,25 +649,7 @@
       <c r="T3" t="b">
         <v>0</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
-      <c r="X3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="U3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -784,26 +718,8 @@
       <c r="T4" t="b">
         <v>0</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>9</v>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -871,26 +787,8 @@
       <c r="T5" t="b">
         <v>0</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
-      </c>
-      <c r="X5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>9</v>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -958,26 +856,8 @@
       <c r="T6" t="b">
         <v>0</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" t="b">
-        <v>0</v>
-      </c>
-      <c r="X6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>9</v>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1041,25 +921,7 @@
       <c r="T7" t="b">
         <v>0</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" t="b">
-        <v>0</v>
-      </c>
-      <c r="X7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="U7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1124,25 +986,7 @@
       <c r="T8" t="b">
         <v>0</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="U8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1207,25 +1051,7 @@
       <c r="T9" t="b">
         <v>0</v>
       </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="U9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1290,25 +1116,7 @@
       <c r="T10" t="b">
         <v>0</v>
       </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" t="b">
-        <v>0</v>
-      </c>
-      <c r="X10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="U10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1373,25 +1181,7 @@
       <c r="T11" t="b">
         <v>0</v>
       </c>
-      <c r="U11" t="b">
-        <v>0</v>
-      </c>
-      <c r="V11" t="b">
-        <v>0</v>
-      </c>
-      <c r="W11" t="b">
-        <v>0</v>
-      </c>
-      <c r="X11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="U11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1456,25 +1246,7 @@
       <c r="T12" t="b">
         <v>0</v>
       </c>
-      <c r="U12" t="b">
-        <v>0</v>
-      </c>
-      <c r="V12" t="b">
-        <v>0</v>
-      </c>
-      <c r="W12" t="b">
-        <v>0</v>
-      </c>
-      <c r="X12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="U12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1535,25 +1307,7 @@
       <c r="T13" t="b">
         <v>0</v>
       </c>
-      <c r="U13" t="b">
-        <v>0</v>
-      </c>
-      <c r="V13" t="b">
-        <v>0</v>
-      </c>
-      <c r="W13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="U13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1622,26 +1376,8 @@
       <c r="T14" t="b">
         <v>0</v>
       </c>
-      <c r="U14" t="b">
-        <v>0</v>
-      </c>
-      <c r="V14" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>9</v>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1705,25 +1441,7 @@
       <c r="T15" t="b">
         <v>0</v>
       </c>
-      <c r="U15" t="b">
-        <v>0</v>
-      </c>
-      <c r="V15" t="b">
-        <v>0</v>
-      </c>
-      <c r="W15" t="b">
-        <v>0</v>
-      </c>
-      <c r="X15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="U15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1788,25 +1506,7 @@
       <c r="T16" t="b">
         <v>0</v>
       </c>
-      <c r="U16" t="b">
-        <v>0</v>
-      </c>
-      <c r="V16" t="b">
-        <v>0</v>
-      </c>
-      <c r="W16" t="b">
-        <v>0</v>
-      </c>
-      <c r="X16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="U16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1871,25 +1571,7 @@
       <c r="T17" t="b">
         <v>0</v>
       </c>
-      <c r="U17" t="b">
-        <v>0</v>
-      </c>
-      <c r="V17" t="b">
-        <v>0</v>
-      </c>
-      <c r="W17" t="b">
-        <v>0</v>
-      </c>
-      <c r="X17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="U17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1954,25 +1636,7 @@
       <c r="T18" t="b">
         <v>0</v>
       </c>
-      <c r="U18" t="b">
-        <v>0</v>
-      </c>
-      <c r="V18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="U18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2037,25 +1701,7 @@
       <c r="T19" t="b">
         <v>0</v>
       </c>
-      <c r="U19" t="b">
-        <v>0</v>
-      </c>
-      <c r="V19" t="b">
-        <v>0</v>
-      </c>
-      <c r="W19" t="b">
-        <v>0</v>
-      </c>
-      <c r="X19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="U19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2120,25 +1766,7 @@
       <c r="T20" t="b">
         <v>0</v>
       </c>
-      <c r="U20" t="b">
-        <v>0</v>
-      </c>
-      <c r="V20" t="b">
-        <v>0</v>
-      </c>
-      <c r="W20" t="b">
-        <v>0</v>
-      </c>
-      <c r="X20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="U20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2203,25 +1831,7 @@
       <c r="T21" t="b">
         <v>0</v>
       </c>
-      <c r="U21" t="b">
-        <v>0</v>
-      </c>
-      <c r="V21" t="b">
-        <v>0</v>
-      </c>
-      <c r="W21" t="b">
-        <v>0</v>
-      </c>
-      <c r="X21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="U21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2286,25 +1896,7 @@
       <c r="T22" t="b">
         <v>0</v>
       </c>
-      <c r="U22" t="b">
-        <v>0</v>
-      </c>
-      <c r="V22" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="U22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2373,25 +1965,7 @@
       <c r="T23" t="b">
         <v>0</v>
       </c>
-      <c r="U23" t="b">
-        <v>0</v>
-      </c>
-      <c r="V23" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="U23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2460,25 +2034,7 @@
       <c r="T24" t="b">
         <v>0</v>
       </c>
-      <c r="U24" t="b">
-        <v>0</v>
-      </c>
-      <c r="V24" t="b">
-        <v>0</v>
-      </c>
-      <c r="W24" t="b">
-        <v>0</v>
-      </c>
-      <c r="X24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="U24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2543,25 +2099,7 @@
       <c r="T25" t="b">
         <v>0</v>
       </c>
-      <c r="U25" t="b">
-        <v>0</v>
-      </c>
-      <c r="V25" t="b">
-        <v>0</v>
-      </c>
-      <c r="W25" t="b">
-        <v>0</v>
-      </c>
-      <c r="X25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="U25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2630,26 +2168,8 @@
       <c r="T26" t="b">
         <v>0</v>
       </c>
-      <c r="U26" t="b">
-        <v>0</v>
-      </c>
-      <c r="V26" t="b">
-        <v>0</v>
-      </c>
-      <c r="W26" t="b">
-        <v>0</v>
-      </c>
-      <c r="X26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>9</v>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2717,26 +2237,8 @@
       <c r="T27" t="b">
         <v>0</v>
       </c>
-      <c r="U27" t="b">
-        <v>0</v>
-      </c>
-      <c r="V27" t="b">
-        <v>0</v>
-      </c>
-      <c r="W27" t="b">
-        <v>0</v>
-      </c>
-      <c r="X27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>9</v>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2800,25 +2302,7 @@
       <c r="T28" t="b">
         <v>0</v>
       </c>
-      <c r="U28" t="b">
-        <v>0</v>
-      </c>
-      <c r="V28" t="b">
-        <v>0</v>
-      </c>
-      <c r="W28" t="b">
-        <v>0</v>
-      </c>
-      <c r="X28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="U28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2883,25 +2367,7 @@
       <c r="T29" t="b">
         <v>0</v>
       </c>
-      <c r="U29" t="b">
-        <v>0</v>
-      </c>
-      <c r="V29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="U29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2970,25 +2436,7 @@
       <c r="T30" t="b">
         <v>0</v>
       </c>
-      <c r="U30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V30" t="b">
-        <v>0</v>
-      </c>
-      <c r="W30" t="b">
-        <v>0</v>
-      </c>
-      <c r="X30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="U30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3057,26 +2505,8 @@
       <c r="T31" t="b">
         <v>0</v>
       </c>
-      <c r="U31" t="b">
-        <v>0</v>
-      </c>
-      <c r="V31" t="b">
-        <v>0</v>
-      </c>
-      <c r="W31" t="b">
-        <v>0</v>
-      </c>
-      <c r="X31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>9</v>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3140,25 +2570,7 @@
       <c r="T32" t="b">
         <v>0</v>
       </c>
-      <c r="U32" t="b">
-        <v>0</v>
-      </c>
-      <c r="V32" t="b">
-        <v>0</v>
-      </c>
-      <c r="W32" t="b">
-        <v>0</v>
-      </c>
-      <c r="X32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="n">
+      <c r="U32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3223,25 +2635,7 @@
       <c r="T33" t="b">
         <v>0</v>
       </c>
-      <c r="U33" t="b">
-        <v>0</v>
-      </c>
-      <c r="V33" t="b">
-        <v>0</v>
-      </c>
-      <c r="W33" t="b">
-        <v>0</v>
-      </c>
-      <c r="X33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA33" t="n">
+      <c r="U33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3310,26 +2704,8 @@
       <c r="T34" t="b">
         <v>0</v>
       </c>
-      <c r="U34" t="b">
-        <v>0</v>
-      </c>
-      <c r="V34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W34" t="b">
-        <v>0</v>
-      </c>
-      <c r="X34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>8</v>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3393,25 +2769,7 @@
       <c r="T35" t="b">
         <v>0</v>
       </c>
-      <c r="U35" t="b">
-        <v>0</v>
-      </c>
-      <c r="V35" t="b">
-        <v>0</v>
-      </c>
-      <c r="W35" t="b">
-        <v>0</v>
-      </c>
-      <c r="X35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="U35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3480,26 +2838,8 @@
       <c r="T36" t="b">
         <v>0</v>
       </c>
-      <c r="U36" t="b">
-        <v>0</v>
-      </c>
-      <c r="V36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W36" t="b">
-        <v>0</v>
-      </c>
-      <c r="X36" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>9</v>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3559,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="b">
         <v>0</v>
@@ -3567,26 +2907,8 @@
       <c r="T37" t="b">
         <v>0</v>
       </c>
-      <c r="U37" t="b">
-        <v>0</v>
-      </c>
-      <c r="V37" t="b">
-        <v>0</v>
-      </c>
-      <c r="W37" t="b">
-        <v>0</v>
-      </c>
-      <c r="X37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>7</v>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3650,25 +2972,7 @@
       <c r="T38" t="b">
         <v>0</v>
       </c>
-      <c r="U38" t="b">
-        <v>0</v>
-      </c>
-      <c r="V38" t="b">
-        <v>0</v>
-      </c>
-      <c r="W38" t="b">
-        <v>0</v>
-      </c>
-      <c r="X38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
+      <c r="U38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3737,26 +3041,8 @@
       <c r="T39" t="b">
         <v>0</v>
       </c>
-      <c r="U39" t="b">
-        <v>0</v>
-      </c>
-      <c r="V39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W39" t="b">
-        <v>0</v>
-      </c>
-      <c r="X39" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>9</v>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3820,25 +3106,7 @@
       <c r="T40" t="b">
         <v>0</v>
       </c>
-      <c r="U40" t="b">
-        <v>0</v>
-      </c>
-      <c r="V40" t="b">
-        <v>0</v>
-      </c>
-      <c r="W40" t="b">
-        <v>0</v>
-      </c>
-      <c r="X40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA40" t="n">
+      <c r="U40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3903,25 +3171,7 @@
       <c r="T41" t="b">
         <v>0</v>
       </c>
-      <c r="U41" t="b">
-        <v>0</v>
-      </c>
-      <c r="V41" t="b">
-        <v>0</v>
-      </c>
-      <c r="W41" t="b">
-        <v>0</v>
-      </c>
-      <c r="X41" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="n">
+      <c r="U41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3985,31 +3235,13 @@
         <v>1</v>
       </c>
       <c r="S42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="b">
         <v>0</v>
       </c>
-      <c r="U42" t="b">
-        <v>0</v>
-      </c>
-      <c r="V42" t="b">
-        <v>0</v>
-      </c>
-      <c r="W42" t="b">
-        <v>0</v>
-      </c>
-      <c r="X42" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y42" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>9</v>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4073,25 +3305,7 @@
       <c r="T43" t="b">
         <v>0</v>
       </c>
-      <c r="U43" t="b">
-        <v>0</v>
-      </c>
-      <c r="V43" t="b">
-        <v>0</v>
-      </c>
-      <c r="W43" t="b">
-        <v>0</v>
-      </c>
-      <c r="X43" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="n">
+      <c r="U43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4156,25 +3370,7 @@
       <c r="T44" t="b">
         <v>0</v>
       </c>
-      <c r="U44" t="b">
-        <v>0</v>
-      </c>
-      <c r="V44" t="b">
-        <v>0</v>
-      </c>
-      <c r="W44" t="b">
-        <v>0</v>
-      </c>
-      <c r="X44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
+      <c r="U44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4239,25 +3435,7 @@
       <c r="T45" t="b">
         <v>0</v>
       </c>
-      <c r="U45" t="b">
-        <v>0</v>
-      </c>
-      <c r="V45" t="b">
-        <v>0</v>
-      </c>
-      <c r="W45" t="b">
-        <v>0</v>
-      </c>
-      <c r="X45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="U45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4322,25 +3500,7 @@
       <c r="T46" t="b">
         <v>0</v>
       </c>
-      <c r="U46" t="b">
-        <v>0</v>
-      </c>
-      <c r="V46" t="b">
-        <v>0</v>
-      </c>
-      <c r="W46" t="b">
-        <v>0</v>
-      </c>
-      <c r="X46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
+      <c r="U46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4405,25 +3565,7 @@
       <c r="T47" t="b">
         <v>0</v>
       </c>
-      <c r="U47" t="b">
-        <v>0</v>
-      </c>
-      <c r="V47" t="b">
-        <v>0</v>
-      </c>
-      <c r="W47" t="b">
-        <v>0</v>
-      </c>
-      <c r="X47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA47" t="n">
+      <c r="U47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4488,25 +3630,7 @@
       <c r="T48" t="b">
         <v>0</v>
       </c>
-      <c r="U48" t="b">
-        <v>0</v>
-      </c>
-      <c r="V48" t="b">
-        <v>0</v>
-      </c>
-      <c r="W48" t="b">
-        <v>0</v>
-      </c>
-      <c r="X48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA48" t="n">
+      <c r="U48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4571,25 +3695,7 @@
       <c r="T49" t="b">
         <v>0</v>
       </c>
-      <c r="U49" t="b">
-        <v>0</v>
-      </c>
-      <c r="V49" t="b">
-        <v>0</v>
-      </c>
-      <c r="W49" t="b">
-        <v>0</v>
-      </c>
-      <c r="X49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA49" t="n">
+      <c r="U49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4654,25 +3760,7 @@
       <c r="T50" t="b">
         <v>0</v>
       </c>
-      <c r="U50" t="b">
-        <v>0</v>
-      </c>
-      <c r="V50" t="b">
-        <v>0</v>
-      </c>
-      <c r="W50" t="b">
-        <v>0</v>
-      </c>
-      <c r="X50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA50" t="n">
+      <c r="U50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4737,25 +3825,7 @@
       <c r="T51" t="b">
         <v>0</v>
       </c>
-      <c r="U51" t="b">
-        <v>0</v>
-      </c>
-      <c r="V51" t="b">
-        <v>0</v>
-      </c>
-      <c r="W51" t="b">
-        <v>0</v>
-      </c>
-      <c r="X51" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA51" t="n">
+      <c r="U51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4820,25 +3890,7 @@
       <c r="T52" t="b">
         <v>0</v>
       </c>
-      <c r="U52" t="b">
-        <v>0</v>
-      </c>
-      <c r="V52" t="b">
-        <v>0</v>
-      </c>
-      <c r="W52" t="b">
-        <v>0</v>
-      </c>
-      <c r="X52" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA52" t="n">
+      <c r="U52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4903,25 +3955,7 @@
       <c r="T53" t="b">
         <v>0</v>
       </c>
-      <c r="U53" t="b">
-        <v>0</v>
-      </c>
-      <c r="V53" t="b">
-        <v>0</v>
-      </c>
-      <c r="W53" t="b">
-        <v>0</v>
-      </c>
-      <c r="X53" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA53" t="n">
+      <c r="U53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4986,25 +4020,7 @@
       <c r="T54" t="b">
         <v>0</v>
       </c>
-      <c r="U54" t="b">
-        <v>0</v>
-      </c>
-      <c r="V54" t="b">
-        <v>0</v>
-      </c>
-      <c r="W54" t="b">
-        <v>0</v>
-      </c>
-      <c r="X54" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA54" t="n">
+      <c r="U54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5069,25 +4085,7 @@
       <c r="T55" t="b">
         <v>0</v>
       </c>
-      <c r="U55" t="b">
-        <v>0</v>
-      </c>
-      <c r="V55" t="b">
-        <v>0</v>
-      </c>
-      <c r="W55" t="b">
-        <v>0</v>
-      </c>
-      <c r="X55" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA55" t="n">
+      <c r="U55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5152,25 +4150,7 @@
       <c r="T56" t="b">
         <v>0</v>
       </c>
-      <c r="U56" t="b">
-        <v>0</v>
-      </c>
-      <c r="V56" t="b">
-        <v>0</v>
-      </c>
-      <c r="W56" t="b">
-        <v>0</v>
-      </c>
-      <c r="X56" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA56" t="n">
+      <c r="U56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5235,25 +4215,7 @@
       <c r="T57" t="b">
         <v>0</v>
       </c>
-      <c r="U57" t="b">
-        <v>0</v>
-      </c>
-      <c r="V57" t="b">
-        <v>0</v>
-      </c>
-      <c r="W57" t="b">
-        <v>0</v>
-      </c>
-      <c r="X57" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA57" t="n">
+      <c r="U57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5318,25 +4280,7 @@
       <c r="T58" t="b">
         <v>0</v>
       </c>
-      <c r="U58" t="b">
-        <v>0</v>
-      </c>
-      <c r="V58" t="b">
-        <v>0</v>
-      </c>
-      <c r="W58" t="b">
-        <v>0</v>
-      </c>
-      <c r="X58" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA58" t="n">
+      <c r="U58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5401,25 +4345,7 @@
       <c r="T59" t="b">
         <v>0</v>
       </c>
-      <c r="U59" t="b">
-        <v>0</v>
-      </c>
-      <c r="V59" t="b">
-        <v>0</v>
-      </c>
-      <c r="W59" t="b">
-        <v>0</v>
-      </c>
-      <c r="X59" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA59" t="n">
+      <c r="U59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5480,25 +4406,7 @@
       <c r="T60" t="b">
         <v>0</v>
       </c>
-      <c r="U60" t="b">
-        <v>0</v>
-      </c>
-      <c r="V60" t="b">
-        <v>0</v>
-      </c>
-      <c r="W60" t="b">
-        <v>0</v>
-      </c>
-      <c r="X60" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA60" t="n">
+      <c r="U60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5563,25 +4471,7 @@
       <c r="T61" t="b">
         <v>0</v>
       </c>
-      <c r="U61" t="b">
-        <v>0</v>
-      </c>
-      <c r="V61" t="b">
-        <v>0</v>
-      </c>
-      <c r="W61" t="b">
-        <v>0</v>
-      </c>
-      <c r="X61" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA61" t="n">
+      <c r="U61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5645,31 +4535,13 @@
         <v>1</v>
       </c>
       <c r="S62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" t="b">
         <v>0</v>
       </c>
-      <c r="U62" t="b">
-        <v>0</v>
-      </c>
-      <c r="V62" t="b">
-        <v>0</v>
-      </c>
-      <c r="W62" t="b">
-        <v>0</v>
-      </c>
-      <c r="X62" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y62" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>7</v>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5733,25 +4605,7 @@
       <c r="T63" t="b">
         <v>0</v>
       </c>
-      <c r="U63" t="b">
-        <v>0</v>
-      </c>
-      <c r="V63" t="b">
-        <v>0</v>
-      </c>
-      <c r="W63" t="b">
-        <v>0</v>
-      </c>
-      <c r="X63" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA63" t="n">
+      <c r="U63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5816,25 +4670,7 @@
       <c r="T64" t="b">
         <v>0</v>
       </c>
-      <c r="U64" t="b">
-        <v>0</v>
-      </c>
-      <c r="V64" t="b">
-        <v>0</v>
-      </c>
-      <c r="W64" t="b">
-        <v>0</v>
-      </c>
-      <c r="X64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA64" t="n">
+      <c r="U64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5903,25 +4739,7 @@
       <c r="T65" t="b">
         <v>0</v>
       </c>
-      <c r="U65" t="b">
-        <v>0</v>
-      </c>
-      <c r="V65" t="b">
-        <v>0</v>
-      </c>
-      <c r="W65" t="b">
-        <v>0</v>
-      </c>
-      <c r="X65" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA65" t="n">
+      <c r="U65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5982,7 +4800,7 @@
         <v>0</v>
       </c>
       <c r="R66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -5990,26 +4808,8 @@
       <c r="T66" t="b">
         <v>0</v>
       </c>
-      <c r="U66" t="b">
-        <v>0</v>
-      </c>
-      <c r="V66" t="b">
-        <v>0</v>
-      </c>
-      <c r="W66" t="b">
-        <v>0</v>
-      </c>
-      <c r="X66" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y66" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>7</v>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -6077,26 +4877,8 @@
       <c r="T67" t="b">
         <v>0</v>
       </c>
-      <c r="U67" t="b">
-        <v>0</v>
-      </c>
-      <c r="V67" t="b">
-        <v>0</v>
-      </c>
-      <c r="W67" t="b">
-        <v>0</v>
-      </c>
-      <c r="X67" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y67" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>7</v>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -6156,25 +4938,7 @@
       <c r="T68" t="b">
         <v>0</v>
       </c>
-      <c r="U68" t="b">
-        <v>0</v>
-      </c>
-      <c r="V68" t="b">
-        <v>0</v>
-      </c>
-      <c r="W68" t="b">
-        <v>0</v>
-      </c>
-      <c r="X68" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA68" t="n">
+      <c r="U68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6239,25 +5003,7 @@
       <c r="T69" t="b">
         <v>0</v>
       </c>
-      <c r="U69" t="b">
-        <v>0</v>
-      </c>
-      <c r="V69" t="b">
-        <v>0</v>
-      </c>
-      <c r="W69" t="b">
-        <v>0</v>
-      </c>
-      <c r="X69" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA69" t="n">
+      <c r="U69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6318,25 +5064,7 @@
       <c r="T70" t="b">
         <v>0</v>
       </c>
-      <c r="U70" t="b">
-        <v>0</v>
-      </c>
-      <c r="V70" t="b">
-        <v>0</v>
-      </c>
-      <c r="W70" t="b">
-        <v>0</v>
-      </c>
-      <c r="X70" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA70" t="n">
+      <c r="U70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6401,25 +5129,7 @@
       <c r="T71" t="b">
         <v>0</v>
       </c>
-      <c r="U71" t="b">
-        <v>0</v>
-      </c>
-      <c r="V71" t="b">
-        <v>0</v>
-      </c>
-      <c r="W71" t="b">
-        <v>0</v>
-      </c>
-      <c r="X71" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA71" t="n">
+      <c r="U71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6483,31 +5193,13 @@
         <v>1</v>
       </c>
       <c r="S72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" t="b">
         <v>0</v>
       </c>
-      <c r="U72" t="b">
-        <v>0</v>
-      </c>
-      <c r="V72" t="b">
-        <v>0</v>
-      </c>
-      <c r="W72" t="b">
-        <v>0</v>
-      </c>
-      <c r="X72" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y72" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>9</v>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6575,25 +5267,7 @@
       <c r="T73" t="b">
         <v>0</v>
       </c>
-      <c r="U73" t="b">
-        <v>0</v>
-      </c>
-      <c r="V73" t="b">
-        <v>0</v>
-      </c>
-      <c r="W73" t="b">
-        <v>0</v>
-      </c>
-      <c r="X73" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y73" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA73" t="n">
+      <c r="U73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6654,25 +5328,7 @@
       <c r="T74" t="b">
         <v>0</v>
       </c>
-      <c r="U74" t="b">
-        <v>0</v>
-      </c>
-      <c r="V74" t="b">
-        <v>0</v>
-      </c>
-      <c r="W74" t="b">
-        <v>0</v>
-      </c>
-      <c r="X74" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y74" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA74" t="n">
+      <c r="U74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6741,26 +5397,8 @@
       <c r="T75" t="b">
         <v>0</v>
       </c>
-      <c r="U75" t="b">
-        <v>0</v>
-      </c>
-      <c r="V75" t="b">
-        <v>0</v>
-      </c>
-      <c r="W75" t="b">
-        <v>0</v>
-      </c>
-      <c r="X75" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y75" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>9</v>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6824,25 +5462,7 @@
       <c r="T76" t="b">
         <v>0</v>
       </c>
-      <c r="U76" t="b">
-        <v>0</v>
-      </c>
-      <c r="V76" t="b">
-        <v>0</v>
-      </c>
-      <c r="W76" t="b">
-        <v>0</v>
-      </c>
-      <c r="X76" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y76" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA76" t="n">
+      <c r="U76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6911,26 +5531,8 @@
       <c r="T77" t="b">
         <v>0</v>
       </c>
-      <c r="U77" t="b">
-        <v>0</v>
-      </c>
-      <c r="V77" t="b">
-        <v>0</v>
-      </c>
-      <c r="W77" t="b">
-        <v>0</v>
-      </c>
-      <c r="X77" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y77" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>9</v>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6994,25 +5596,7 @@
       <c r="T78" t="b">
         <v>0</v>
       </c>
-      <c r="U78" t="b">
-        <v>0</v>
-      </c>
-      <c r="V78" t="b">
-        <v>0</v>
-      </c>
-      <c r="W78" t="b">
-        <v>0</v>
-      </c>
-      <c r="X78" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y78" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z78" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA78" t="n">
+      <c r="U78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7073,25 +5657,7 @@
       <c r="T79" t="b">
         <v>0</v>
       </c>
-      <c r="U79" t="b">
-        <v>0</v>
-      </c>
-      <c r="V79" t="b">
-        <v>0</v>
-      </c>
-      <c r="W79" t="b">
-        <v>0</v>
-      </c>
-      <c r="X79" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA79" t="n">
+      <c r="U79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7156,25 +5722,7 @@
       <c r="T80" t="b">
         <v>0</v>
       </c>
-      <c r="U80" t="b">
-        <v>0</v>
-      </c>
-      <c r="V80" t="b">
-        <v>0</v>
-      </c>
-      <c r="W80" t="b">
-        <v>0</v>
-      </c>
-      <c r="X80" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y80" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA80" t="n">
+      <c r="U80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7239,25 +5787,7 @@
       <c r="T81" t="b">
         <v>0</v>
       </c>
-      <c r="U81" t="b">
-        <v>0</v>
-      </c>
-      <c r="V81" t="b">
-        <v>0</v>
-      </c>
-      <c r="W81" t="b">
-        <v>0</v>
-      </c>
-      <c r="X81" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y81" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA81" t="n">
+      <c r="U81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7322,25 +5852,7 @@
       <c r="T82" t="b">
         <v>0</v>
       </c>
-      <c r="U82" t="b">
-        <v>0</v>
-      </c>
-      <c r="V82" t="b">
-        <v>0</v>
-      </c>
-      <c r="W82" t="b">
-        <v>0</v>
-      </c>
-      <c r="X82" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA82" t="n">
+      <c r="U82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7405,25 +5917,7 @@
       <c r="T83" t="b">
         <v>0</v>
       </c>
-      <c r="U83" t="b">
-        <v>0</v>
-      </c>
-      <c r="V83" t="b">
-        <v>0</v>
-      </c>
-      <c r="W83" t="b">
-        <v>0</v>
-      </c>
-      <c r="X83" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y83" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z83" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA83" t="n">
+      <c r="U83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7484,25 +5978,7 @@
       <c r="T84" t="b">
         <v>0</v>
       </c>
-      <c r="U84" t="b">
-        <v>0</v>
-      </c>
-      <c r="V84" t="b">
-        <v>0</v>
-      </c>
-      <c r="W84" t="b">
-        <v>0</v>
-      </c>
-      <c r="X84" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y84" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA84" t="n">
+      <c r="U84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7563,25 +6039,7 @@
       <c r="T85" t="b">
         <v>0</v>
       </c>
-      <c r="U85" t="b">
-        <v>0</v>
-      </c>
-      <c r="V85" t="b">
-        <v>0</v>
-      </c>
-      <c r="W85" t="b">
-        <v>0</v>
-      </c>
-      <c r="X85" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y85" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA85" t="n">
+      <c r="U85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7646,25 +6104,7 @@
       <c r="T86" t="b">
         <v>0</v>
       </c>
-      <c r="U86" t="b">
-        <v>0</v>
-      </c>
-      <c r="V86" t="b">
-        <v>0</v>
-      </c>
-      <c r="W86" t="b">
-        <v>0</v>
-      </c>
-      <c r="X86" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y86" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA86" t="n">
+      <c r="U86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7733,26 +6173,8 @@
       <c r="T87" t="b">
         <v>0</v>
       </c>
-      <c r="U87" t="b">
-        <v>0</v>
-      </c>
-      <c r="V87" t="b">
-        <v>0</v>
-      </c>
-      <c r="W87" t="b">
-        <v>0</v>
-      </c>
-      <c r="X87" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y87" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA87" t="n">
-        <v>7</v>
+      <c r="U87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -7816,25 +6238,7 @@
       <c r="T88" t="b">
         <v>0</v>
       </c>
-      <c r="U88" t="b">
-        <v>0</v>
-      </c>
-      <c r="V88" t="b">
-        <v>0</v>
-      </c>
-      <c r="W88" t="b">
-        <v>0</v>
-      </c>
-      <c r="X88" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y88" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z88" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA88" t="n">
+      <c r="U88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7899,25 +6303,7 @@
       <c r="T89" t="b">
         <v>0</v>
       </c>
-      <c r="U89" t="b">
-        <v>0</v>
-      </c>
-      <c r="V89" t="b">
-        <v>0</v>
-      </c>
-      <c r="W89" t="b">
-        <v>0</v>
-      </c>
-      <c r="X89" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z89" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA89" t="n">
+      <c r="U89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7982,25 +6368,7 @@
       <c r="T90" t="b">
         <v>0</v>
       </c>
-      <c r="U90" t="b">
-        <v>0</v>
-      </c>
-      <c r="V90" t="b">
-        <v>0</v>
-      </c>
-      <c r="W90" t="b">
-        <v>0</v>
-      </c>
-      <c r="X90" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y90" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA90" t="n">
+      <c r="U90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8065,25 +6433,7 @@
       <c r="T91" t="b">
         <v>0</v>
       </c>
-      <c r="U91" t="b">
-        <v>0</v>
-      </c>
-      <c r="V91" t="b">
-        <v>0</v>
-      </c>
-      <c r="W91" t="b">
-        <v>0</v>
-      </c>
-      <c r="X91" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y91" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z91" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA91" t="n">
+      <c r="U91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8148,25 +6498,7 @@
       <c r="T92" t="b">
         <v>0</v>
       </c>
-      <c r="U92" t="b">
-        <v>0</v>
-      </c>
-      <c r="V92" t="b">
-        <v>0</v>
-      </c>
-      <c r="W92" t="b">
-        <v>0</v>
-      </c>
-      <c r="X92" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y92" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z92" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA92" t="n">
+      <c r="U92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8230,31 +6562,13 @@
         <v>1</v>
       </c>
       <c r="S93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" t="b">
         <v>0</v>
       </c>
-      <c r="U93" t="b">
-        <v>0</v>
-      </c>
-      <c r="V93" t="b">
-        <v>0</v>
-      </c>
-      <c r="W93" t="b">
-        <v>0</v>
-      </c>
-      <c r="X93" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y93" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>9</v>
+      <c r="U93" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -8318,25 +6632,7 @@
       <c r="T94" t="b">
         <v>0</v>
       </c>
-      <c r="U94" t="b">
-        <v>0</v>
-      </c>
-      <c r="V94" t="b">
-        <v>0</v>
-      </c>
-      <c r="W94" t="b">
-        <v>0</v>
-      </c>
-      <c r="X94" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y94" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA94" t="n">
+      <c r="U94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8405,26 +6701,8 @@
       <c r="T95" t="b">
         <v>0</v>
       </c>
-      <c r="U95" t="b">
-        <v>1</v>
-      </c>
-      <c r="V95" t="b">
-        <v>0</v>
-      </c>
-      <c r="W95" t="b">
-        <v>1</v>
-      </c>
-      <c r="X95" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y95" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA95" t="n">
-        <v>1</v>
+      <c r="U95" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -8488,25 +6766,7 @@
       <c r="T96" t="b">
         <v>0</v>
       </c>
-      <c r="U96" t="b">
-        <v>0</v>
-      </c>
-      <c r="V96" t="b">
-        <v>0</v>
-      </c>
-      <c r="W96" t="b">
-        <v>0</v>
-      </c>
-      <c r="X96" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y96" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z96" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA96" t="n">
+      <c r="U96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8575,26 +6835,8 @@
       <c r="T97" t="b">
         <v>0</v>
       </c>
-      <c r="U97" t="b">
-        <v>0</v>
-      </c>
-      <c r="V97" t="b">
-        <v>0</v>
-      </c>
-      <c r="W97" t="b">
-        <v>0</v>
-      </c>
-      <c r="X97" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y97" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA97" t="n">
-        <v>9</v>
+      <c r="U97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -8654,25 +6896,7 @@
       <c r="T98" t="b">
         <v>0</v>
       </c>
-      <c r="U98" t="b">
-        <v>0</v>
-      </c>
-      <c r="V98" t="b">
-        <v>0</v>
-      </c>
-      <c r="W98" t="b">
-        <v>0</v>
-      </c>
-      <c r="X98" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y98" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z98" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA98" t="n">
+      <c r="U98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8741,26 +6965,8 @@
       <c r="T99" t="b">
         <v>0</v>
       </c>
-      <c r="U99" t="b">
-        <v>0</v>
-      </c>
-      <c r="V99" t="b">
-        <v>0</v>
-      </c>
-      <c r="W99" t="b">
-        <v>0</v>
-      </c>
-      <c r="X99" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y99" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA99" t="n">
-        <v>7</v>
+      <c r="U99" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -8820,25 +7026,7 @@
       <c r="T100" t="b">
         <v>0</v>
       </c>
-      <c r="U100" t="b">
-        <v>0</v>
-      </c>
-      <c r="V100" t="b">
-        <v>0</v>
-      </c>
-      <c r="W100" t="b">
-        <v>0</v>
-      </c>
-      <c r="X100" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y100" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z100" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA100" t="n">
+      <c r="U100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8903,25 +7091,7 @@
       <c r="T101" t="b">
         <v>0</v>
       </c>
-      <c r="U101" t="b">
-        <v>0</v>
-      </c>
-      <c r="V101" t="b">
-        <v>0</v>
-      </c>
-      <c r="W101" t="b">
-        <v>0</v>
-      </c>
-      <c r="X101" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA101" t="n">
+      <c r="U101" t="n">
         <v>0</v>
       </c>
     </row>
